--- a/tests/Fixtures/altdaten/mitglieder.xlsx
+++ b/tests/Fixtures/altdaten/mitglieder.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t xml:space="preserve">LfdNr</t>
   </si>
@@ -511,6 +511,30 @@
   </si>
   <si>
     <t xml:space="preserve">01.01.2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02.02.1992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leipzighausen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unterwegs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.03.1973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atlantis</t>
   </si>
   <si>
     <t xml:space="preserve">Zweites Blatt</t>
@@ -2371,6 +2395,118 @@
         <v>0</v>
       </c>
       <c r="AV28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29">
+        <v>1029</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>168</v>
+      </c>
+      <c r="G29" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" t="s">
+        <v>169</v>
+      </c>
+      <c r="J29" t="s">
+        <v>53</v>
+      </c>
+      <c r="K29">
+        <v>4109</v>
+      </c>
+      <c r="L29" t="s">
+        <v>170</v>
+      </c>
+      <c r="M29" t="s">
+        <v>55</v>
+      </c>
+      <c r="S29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF29">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30">
+        <v>1030</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" t="s">
+        <v>172</v>
+      </c>
+      <c r="G30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" t="s">
+        <v>173</v>
+      </c>
+      <c r="J30" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30">
+        <v>80331</v>
+      </c>
+      <c r="L30" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" t="s">
+        <v>174</v>
+      </c>
+      <c r="S30" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF30">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
         <v>0</v>
       </c>
     </row>
@@ -2394,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
